--- a/evidence-room/03_AP_AGENT_OS_PRO/Spreadsheets/ER_AP_Controls_Matrix.xlsx
+++ b/evidence-room/03_AP_AGENT_OS_PRO/Spreadsheets/ER_AP_Controls_Matrix.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONTROL_MATRIX" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MATRIX_FULL" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -82,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -92,6 +93,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -862,4 +866,574 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Preventive/Detective</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Human owner</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Escalation trigger</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>01 Intake</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Silent drop</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Channel count vs stub log</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>AP Operations</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Intake reconciliation</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Count gap &gt; 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>01 Intake</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Extract invented</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Citation + confidence floors</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>AP Operations</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Gold-label sample</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Ready field without citation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>03 Matching</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Qty &gt; received</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>3-way / GR tests</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Match Lead</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>GR snapshot</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Weekly / 100% pilot</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Posted over-received</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>03 Matching</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Invented GR or PO</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>No write tools</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Systems</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Tool allow-list</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Each release</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Write attempt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>10 Dup/Anomaly</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Flag treated as fraud verdict</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Hypothesis language only</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Detective</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Controls</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Flag pack wording</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>“Fraud” in output</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>12 Payment review</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Agent releases payment</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>No release tool; dual humans</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Treasury</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Payment log vs agent id</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Each run</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Agent id on release</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>12 Payment review</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Bank change executed</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>EX-BNK flag only</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Controller</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Bank-change ticket</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Continuous</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Master write by agent</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>16 Orchestrator</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Work object without owner</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>SLA clock requires named human</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Process owner</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Ageing by owner</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Parked-without-owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Prompt injection</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Content/instruction split; no arbitrary fetch</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Test lead</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Injection pack</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Each release</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Injection success</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Unofficial copilot</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Autonomy register + discovery</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Detective</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Process owner</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Register vs observed</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Helper not on register</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Model change silent</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Version pin + recert</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Systems</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Change record</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Each change</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Untracked model id</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>SoD collision</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Agent cannot hold A; payment dual-human</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Preventive</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Controller</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>RACI sample</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Agent listed as Accountable</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>